--- a/examples/carry-forward/规则_决策表.xlsx
+++ b/examples/carry-forward/规则_决策表.xlsx
@@ -7,11 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="输入" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="设置" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="字段组" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="决策表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="测试" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="设置" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="字段组" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="决策表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="测试" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,12 +45,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -98,23 +97,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -125,7 +124,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -511,11 +510,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
@@ -524,75 +523,108 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>基准日期</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>本批例会日: 决策表里 =基准日期 就是它, 也是内嵌测试用的日期。每批跑的时候用 --var 基准日期=... 给真实的例会日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>output/本期全量_更新后.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>本期</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>本期全量.xlsx</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 本期.本批冒泡</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>上期全量.xlsx</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>上一批次的全量表, 按 岗位编码 对齐到主表; 上期.存在 = 上批有没有这个岗位</t>
         </is>
@@ -604,74 +636,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="63" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>设置项</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>值</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>基准日期</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>46315</v>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>本批例会日: 决策表里 =基准日期 就是它。固定下来每次跑结果一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>output/本期全量_更新后.xlsx</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -686,34 +650,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>列名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2" ht="47" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>会议记录</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>例会时间, 类别-会议, 状态-会议, 例会结论, 备注, 待跟进事宜</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>给这六列起个名字。决策表里以 会议记录 为列名的输出格: 写 上期 = 组内每列从上期的同名列复制; 写 清空 = 整组清空; - = 不改。同一条规则显式写了的列以显式为准 (R1 的 例会时间, R3 的 状态-会议)</t>
         </is>
@@ -724,7 +688,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -745,17 +709,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>首次命中</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>三条规则互斥, 每行最多命中一条; 不冒泡且上批没有记录的岗位什么都不动。本批冒泡 是文本列, 格里的 是 / 否 是文字</t>
         </is>
@@ -894,7 +858,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>本批冒泡且上批有记录: 会议记录整组从上期带入, 例会时间改成本批例会日 (显式写的列优先于字段组里的同名列)</t>
         </is>
@@ -939,7 +903,7 @@
           <t>01-新增</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>首次冒泡: 记例会时间, 状态 01-新增</t>
         </is>
@@ -984,7 +948,7 @@
           <t>06-本批未冒泡</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>上批冒泡、本批没冒泡且上批还没关闭: 历史记录整组带入 (例会时间也是上批的), 状态标成 06。已关闭的不动</t>
         </is>
@@ -995,7 +959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1270,7 +1234,7 @@
           <t>确认任命时间</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>冒泡且上批有: 六列整组带入, 例会时间是本批的 (基准日期) 而不是上批的</t>
         </is>
@@ -1311,7 +1275,7 @@
       <c r="N4" s="13" t="n"/>
       <c r="O4" s="13" t="n"/>
       <c r="P4" s="13" t="n"/>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>冒泡且上批没有: 首次冒泡</t>
         </is>
@@ -1382,7 +1346,7 @@
           <t>跟进到位情况</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>不冒泡且上批有未关闭记录: 整组带入, 例会时间是上批的, 状态标 06</t>
         </is>
@@ -1417,7 +1381,7 @@
       <c r="N6" s="13" t="n"/>
       <c r="O6" s="13" t="n"/>
       <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>不冒泡且上批没有: 不动</t>
         </is>
@@ -1496,7 +1460,7 @@
           <t>走审批</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>本期备注原来有值、上期为空: 整组带入会把它清成空 (期望格写 空)</t>
         </is>
@@ -1543,7 +1507,7 @@
       <c r="N8" s="13" t="n"/>
       <c r="O8" s="13" t="n"/>
       <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>不冒泡且上批已关闭: R3 的 != 05-已关闭 不成立, 不动</t>
         </is>

--- a/examples/carry-forward/规则_决策表.xlsx
+++ b/examples/carry-forward/规则_决策表.xlsx
@@ -95,17 +95,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -113,6 +113,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -510,121 +513,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30.4" customWidth="1" min="2" max="2"/>
+    <col width="10.8" customWidth="1" min="3" max="3"/>
+    <col width="15.8" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>基准日期</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n">
-        <v>46315</v>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>本批例会日: 决策表里 =基准日期 就是它, 也是内嵌测试用的日期。每批跑的时候用 --var 基准日期=... 给真实的例会日</t>
+          <t>设置项</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>每行一项: A 列名字 / B 列值 / 再往右是说明; 只认 基准日期 / 输出, 写别的加载时报错; B 列留空 = 取默认值</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
+          <t>基准日期</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>本批例会日: 决策表里 =基准日期 就是它, 也是内嵌测试用的日期。每批跑的时候用 --var 基准日期=... 给真实的例会日</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>output/本期全量_更新后.xlsx</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>匹配</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>重复键</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>文件</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>输入表</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>下一行是列名, 之后每行声明一个输入: 名称 = 规则里的前缀; 匹配 = 主表写 主表, 其它写对齐到主表的键; 文件 = 默认文件 (命令行 -i 可覆盖)。输入表下面不要再写别的</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>匹配</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>重复键</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>文件</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>本期</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>本期全量.xlsx</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 本期.本批冒泡</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>上期全量.xlsx</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>上一批次的全量表, 按 岗位编码 对齐到主表; 上期.存在 = 上批有没有这个岗位</t>
         </is>
@@ -644,8 +671,8 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10.8" customWidth="1" min="1" max="1"/>
+    <col width="64.59999999999999" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -672,7 +699,7 @@
           <t>会议记录</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>例会时间, 类别-会议, 状态-会议, 例会结论, 备注, 待跟进事宜</t>
         </is>
@@ -697,14 +724,14 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="10.8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16.2" customWidth="1" min="3" max="3"/>
+    <col width="11.8" customWidth="1" min="4" max="4"/>
+    <col width="17.2" customWidth="1" min="5" max="5"/>
+    <col width="10.8" customWidth="1" min="6" max="6"/>
+    <col width="11.8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -714,146 +741,146 @@
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>首次命中</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>三条规则互斥, 每行最多命中一条; 不冒泡且上批没有记录的岗位什么都不动。本批冒泡 是文本列, 格里的 是 / 否 是文字</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>本期.本批冒泡</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>上期.存在</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>上期.状态-会议</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>会议记录</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>例会时间</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>状态-会议</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>=基准日期</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -865,85 +892,85 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>=基准日期</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>首次冒泡: 记例会时间, 状态 01-新增</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>!= 05-已关闭</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>06-本批未冒泡</t>
         </is>
@@ -969,267 +996,267 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="16.2" customWidth="1" min="2" max="2"/>
+    <col width="11.8" customWidth="1" min="3" max="3"/>
+    <col width="16.2" customWidth="1" min="4" max="4"/>
+    <col width="17.2" customWidth="1" min="5" max="5"/>
+    <col width="17.2" customWidth="1" min="6" max="6"/>
+    <col width="16.2" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="18.4" customWidth="1" min="9" max="9"/>
+    <col width="11.8" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="11.8" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="10.8" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="15.2" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="Q1" s="11" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>本期.本批冒泡</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>上期.存在</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>上期.例会时间</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>上期.类别-会议</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>上期.状态-会议</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>上期.例会结论</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>上期.备注</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>上期.待跟进事宜</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>本期.备注</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="K2" s="10" t="inlineStr">
         <is>
           <t>例会时间</t>
         </is>
       </c>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>类别-会议</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>状态-会议</t>
         </is>
       </c>
-      <c r="N2" s="9" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>例会结论</t>
         </is>
       </c>
-      <c r="O2" s="9" t="inlineStr">
+      <c r="O2" s="10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="P2" s="9" t="inlineStr">
+      <c r="P2" s="10" t="inlineStr">
         <is>
           <t>待跟进事宜</t>
         </is>
       </c>
-      <c r="Q2" s="10" t="inlineStr">
+      <c r="Q2" s="11" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="16" t="n">
         <v>46285</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>同意推进</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>候选人待定</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>确认任命时间</t>
         </is>
       </c>
-      <c r="J3" s="12" t="n"/>
-      <c r="K3" s="16" t="n">
+      <c r="J3" s="13" t="n"/>
+      <c r="K3" s="17" t="n">
         <v>46315</v>
       </c>
-      <c r="L3" s="13" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="M3" s="13" t="inlineStr">
+      <c r="M3" s="14" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="N3" s="13" t="inlineStr">
+      <c r="N3" s="14" t="inlineStr">
         <is>
           <t>同意推进</t>
         </is>
       </c>
-      <c r="O3" s="13" t="inlineStr">
+      <c r="O3" s="14" t="inlineStr">
         <is>
           <t>候选人待定</t>
         </is>
       </c>
-      <c r="P3" s="13" t="inlineStr">
+      <c r="P3" s="14" t="inlineStr">
         <is>
           <t>确认任命时间</t>
         </is>
@@ -1241,107 +1268,107 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="12" t="n"/>
-      <c r="J4" s="12" t="n"/>
-      <c r="K4" s="16" t="n">
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="13" t="n"/>
+      <c r="J4" s="13" t="n"/>
+      <c r="K4" s="17" t="n">
         <v>46315</v>
       </c>
-      <c r="L4" s="13" t="n"/>
-      <c r="M4" s="13" t="inlineStr">
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="N4" s="13" t="n"/>
-      <c r="O4" s="13" t="n"/>
-      <c r="P4" s="13" t="n"/>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>冒泡且上批没有: 首次冒泡</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="16" t="n">
         <v>46285</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>按计划</t>
         </is>
       </c>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>跟进到位情况</t>
         </is>
       </c>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="16" t="n">
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="17" t="n">
         <v>46285</v>
       </c>
-      <c r="L5" s="13" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="M5" s="13" t="inlineStr">
+      <c r="M5" s="14" t="inlineStr">
         <is>
           <t>06-本批未冒泡</t>
         </is>
       </c>
-      <c r="N5" s="13" t="inlineStr">
+      <c r="N5" s="14" t="inlineStr">
         <is>
           <t>按计划</t>
         </is>
       </c>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="inlineStr">
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="inlineStr">
         <is>
           <t>跟进到位情况</t>
         </is>
@@ -1353,109 +1380,109 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="13" t="n"/>
-      <c r="O6" s="13" t="n"/>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>不冒泡且上批没有: 不动</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>46285</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>面谈通过</t>
         </is>
       </c>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>走审批</t>
         </is>
       </c>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>临时备注</t>
         </is>
       </c>
-      <c r="K7" s="16" t="n">
+      <c r="K7" s="17" t="n">
         <v>46315</v>
       </c>
-      <c r="L7" s="13" t="inlineStr">
+      <c r="L7" s="14" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="M7" s="13" t="inlineStr">
+      <c r="M7" s="14" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="N7" s="13" t="inlineStr">
+      <c r="N7" s="14" t="inlineStr">
         <is>
           <t>面谈通过</t>
         </is>
       </c>
-      <c r="O7" s="13" t="inlineStr">
+      <c r="O7" s="14" t="inlineStr">
         <is>
           <t>空</t>
         </is>
       </c>
-      <c r="P7" s="13" t="inlineStr">
+      <c r="P7" s="14" t="inlineStr">
         <is>
           <t>走审批</t>
         </is>
@@ -1467,47 +1494,47 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>05-已关闭</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>已任命</t>
         </is>
       </c>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="13" t="n"/>
-      <c r="O8" s="13" t="n"/>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="3" t="inlineStr">
+      <c r="H8" s="13" t="n"/>
+      <c r="I8" s="13" t="n"/>
+      <c r="J8" s="13" t="n"/>
+      <c r="K8" s="14" t="n"/>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="14" t="n"/>
+      <c r="N8" s="14" t="n"/>
+      <c r="O8" s="14" t="n"/>
+      <c r="P8" s="14" t="n"/>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>不冒泡且上批已关闭: R3 的 != 05-已关闭 不成立, 不动</t>
         </is>

--- a/examples/carry-forward/规则_决策表.xlsx
+++ b/examples/carry-forward/规则_决策表.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,15 +33,27 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font/>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -69,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -91,61 +103,116 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -523,141 +590,157 @@
     <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>设置项</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>每行一项: A 列名字 / B 列值 / 再往右是说明; 只认 基准日期 / 输出, 写别的加载时报错; B 列留空 = 取默认值</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="5" t="n"/>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>基准日期</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="7" t="n">
         <v>46315</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>本批例会日: 决策表里 =基准日期 就是它, 也是内嵌测试用的日期。每批跑的时候用 --var 基准日期=... 给真实的例会日</t>
         </is>
       </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>output/本期全量_更新后.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖</t>
         </is>
       </c>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="5" t="n"/>
     </row>
     <row r="4"/>
-    <row r="5">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>输入表</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>下一行是列名, 之后每行声明一个输入: 名称 = 规则里的前缀; 匹配 = 主表写 主表, 其它写对齐到主表的键; 文件 = 默认文件 (命令行 -i 可覆盖)。输入表下面不要再写别的</t>
         </is>
       </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>本期</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>本期全量.xlsx</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 本期.本批冒泡</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>上期全量.xlsx</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>上一批次的全量表, 按 岗位编码 对齐到主表; 上期.存在 = 上批有没有这个岗位</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C5:E5"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -677,34 +760,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>列名</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2" ht="47" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>会议记录</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>例会时间, 类别-会议, 状态-会议, 例会结论, 备注, 待跟进事宜</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>给这六列起个名字。决策表里以 会议记录 为列名的输出格: 写 上期 = 组内每列从上期的同名列复制; 写 清空 = 整组清空; - = 不改。同一条规则显式写了的列以显式为准 (R1 的 例会时间, R3 的 状态-会议)</t>
         </is>
@@ -736,252 +819,261 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>首次命中</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>三条规则互斥, 每行最多命中一条; 不冒泡且上批没有记录的岗位什么都不动。本批冒泡 是文本列, 格里的 是 / 否 是文字</t>
         </is>
       </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>本期.本批冒泡</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>上期.存在</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>上期.状态-会议</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>会议记录</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>例会时间</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>状态-会议</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>=基准日期</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>本批冒泡且上批有记录: 会议记录整组从上期带入, 例会时间改成本批例会日 (显式写的列优先于字段组里的同名列)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>=基准日期</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>首次冒泡: 记例会时间, 状态 01-新增</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>!= 05-已关闭</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>06-本批未冒泡</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>上批冒泡、本批没冒泡且上批还没关闭: 历史记录整组带入 (例会时间也是上批的), 状态标成 06。已关闭的不动</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1015,526 +1107,526 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="O1" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="P1" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="Q1" s="11" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>本期.本批冒泡</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>上期.存在</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>上期.例会时间</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>上期.类别-会议</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>上期.状态-会议</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>上期.例会结论</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>上期.备注</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>上期.待跟进事宜</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>本期.备注</t>
         </is>
       </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="K2" s="14" t="inlineStr">
         <is>
           <t>例会时间</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="L2" s="14" t="inlineStr">
         <is>
           <t>类别-会议</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr">
+      <c r="M2" s="14" t="inlineStr">
         <is>
           <t>状态-会议</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr">
+      <c r="N2" s="14" t="inlineStr">
         <is>
           <t>例会结论</t>
         </is>
       </c>
-      <c r="O2" s="10" t="inlineStr">
+      <c r="O2" s="14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="P2" s="10" t="inlineStr">
+      <c r="P2" s="14" t="inlineStr">
         <is>
           <t>待跟进事宜</t>
         </is>
       </c>
-      <c r="Q2" s="11" t="inlineStr">
+      <c r="Q2" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="21" t="n">
         <v>46285</v>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>同意推进</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>候选人待定</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>确认任命时间</t>
         </is>
       </c>
-      <c r="J3" s="13" t="n"/>
-      <c r="K3" s="17" t="n">
+      <c r="J3" s="17" t="n"/>
+      <c r="K3" s="22" t="n">
         <v>46315</v>
       </c>
-      <c r="L3" s="14" t="inlineStr">
+      <c r="L3" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="M3" s="14" t="inlineStr">
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="N3" s="14" t="inlineStr">
+      <c r="N3" s="18" t="inlineStr">
         <is>
           <t>同意推进</t>
         </is>
       </c>
-      <c r="O3" s="14" t="inlineStr">
+      <c r="O3" s="18" t="inlineStr">
         <is>
           <t>候选人待定</t>
         </is>
       </c>
-      <c r="P3" s="14" t="inlineStr">
+      <c r="P3" s="18" t="inlineStr">
         <is>
           <t>确认任命时间</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="8" t="inlineStr">
         <is>
           <t>冒泡且上批有: 六列整组带入, 例会时间是本批的 (基准日期) 而不是上批的</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="13" t="n"/>
-      <c r="H4" s="13" t="n"/>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="13" t="n"/>
-      <c r="K4" s="17" t="n">
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
+      <c r="G4" s="17" t="n"/>
+      <c r="H4" s="17" t="n"/>
+      <c r="I4" s="17" t="n"/>
+      <c r="J4" s="17" t="n"/>
+      <c r="K4" s="22" t="n">
         <v>46315</v>
       </c>
-      <c r="L4" s="14" t="n"/>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="L4" s="18" t="n"/>
+      <c r="M4" s="18" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="N4" s="14" t="n"/>
-      <c r="O4" s="14" t="n"/>
-      <c r="P4" s="14" t="n"/>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="N4" s="18" t="n"/>
+      <c r="O4" s="18" t="n"/>
+      <c r="P4" s="18" t="n"/>
+      <c r="Q4" s="20" t="inlineStr">
         <is>
           <t>冒泡且上批没有: 首次冒泡</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="21" t="n">
         <v>46285</v>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>按计划</t>
         </is>
       </c>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="H5" s="17" t="n"/>
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>跟进到位情况</t>
         </is>
       </c>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="17" t="n">
+      <c r="J5" s="17" t="n"/>
+      <c r="K5" s="22" t="n">
         <v>46285</v>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="L5" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr">
+      <c r="M5" s="18" t="inlineStr">
         <is>
           <t>06-本批未冒泡</t>
         </is>
       </c>
-      <c r="N5" s="14" t="inlineStr">
+      <c r="N5" s="18" t="inlineStr">
         <is>
           <t>按计划</t>
         </is>
       </c>
-      <c r="O5" s="14" t="n"/>
-      <c r="P5" s="14" t="inlineStr">
+      <c r="O5" s="18" t="n"/>
+      <c r="P5" s="18" t="inlineStr">
         <is>
           <t>跟进到位情况</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="8" t="inlineStr">
         <is>
           <t>不冒泡且上批有未关闭记录: 整组带入, 例会时间是上批的, 状态标 06</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="14" t="n"/>
-      <c r="L6" s="14" t="n"/>
-      <c r="M6" s="14" t="n"/>
-      <c r="N6" s="14" t="n"/>
-      <c r="O6" s="14" t="n"/>
-      <c r="P6" s="14" t="n"/>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="n"/>
+      <c r="I6" s="17" t="n"/>
+      <c r="J6" s="17" t="n"/>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="18" t="n"/>
+      <c r="M6" s="18" t="n"/>
+      <c r="N6" s="18" t="n"/>
+      <c r="O6" s="18" t="n"/>
+      <c r="P6" s="18" t="n"/>
+      <c r="Q6" s="20" t="inlineStr">
         <is>
           <t>不冒泡且上批没有: 不动</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="21" t="n">
         <v>46285</v>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>面谈通过</t>
         </is>
       </c>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>走审批</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>临时备注</t>
         </is>
       </c>
-      <c r="K7" s="17" t="n">
+      <c r="K7" s="22" t="n">
         <v>46315</v>
       </c>
-      <c r="L7" s="14" t="inlineStr">
+      <c r="L7" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="M7" s="14" t="inlineStr">
+      <c r="M7" s="18" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="N7" s="14" t="inlineStr">
+      <c r="N7" s="18" t="inlineStr">
         <is>
           <t>面谈通过</t>
         </is>
       </c>
-      <c r="O7" s="14" t="inlineStr">
+      <c r="O7" s="18" t="inlineStr">
         <is>
           <t>空</t>
         </is>
       </c>
-      <c r="P7" s="14" t="inlineStr">
+      <c r="P7" s="18" t="inlineStr">
         <is>
           <t>走审批</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="8" t="inlineStr">
         <is>
           <t>本期备注原来有值、上期为空: 整组带入会把它清成空 (期望格写 空)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>05-已关闭</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>已任命</t>
         </is>
       </c>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="14" t="n"/>
-      <c r="L8" s="14" t="n"/>
-      <c r="M8" s="14" t="n"/>
-      <c r="N8" s="14" t="n"/>
-      <c r="O8" s="14" t="n"/>
-      <c r="P8" s="14" t="n"/>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="H8" s="17" t="n"/>
+      <c r="I8" s="17" t="n"/>
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="18" t="n"/>
+      <c r="M8" s="18" t="n"/>
+      <c r="N8" s="18" t="n"/>
+      <c r="O8" s="18" t="n"/>
+      <c r="P8" s="18" t="n"/>
+      <c r="Q8" s="20" t="inlineStr">
         <is>
           <t>不冒泡且上批已关闭: R3 的 != 05-已关闭 不成立, 不动</t>
         </is>

--- a/examples/carry-forward/规则_决策表.xlsx
+++ b/examples/carry-forward/规则_决策表.xlsx
@@ -167,9 +167,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -207,6 +204,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -605,18 +605,15 @@
       <c r="D1" s="4" t="n"/>
       <c r="E1" s="5" t="n"/>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="47" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>基准日期</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
-        <v>46315</v>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>本批例会日: 决策表里 =基准日期 就是它, 也是内嵌测试用的日期。每批跑的时候用 --var 基准日期=... 给真实的例会日</t>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>本批例会日: 决策表里 =基准日期 就是它。每批不同, 跑的时候给: --var 基准日期=2026-10-20 (Python: variables=); 这里留空, 没给就取运行当天。内嵌测试的日期写在「测试」sheet 表头上方, 与这里无关</t>
         </is>
       </c>
       <c r="D2" s="4" t="n"/>
@@ -628,12 +625,12 @@
           <t>输出</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>output/本期全量_更新后.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖</t>
         </is>
@@ -658,27 +655,27 @@
       <c r="E5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -690,18 +687,18 @@
           <t>本期</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>本期全量.xlsx</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 本期.本批冒泡</t>
         </is>
@@ -713,22 +710,22 @@
           <t>上期</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>上期全量.xlsx</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>上一批次的全量表, 按 岗位编码 对齐到主表; 上期.存在 = 上批有没有这个岗位</t>
         </is>
@@ -760,17 +757,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>列名</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -782,12 +779,12 @@
           <t>会议记录</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>例会时间, 类别-会议, 状态-会议, 例会结论, 备注, 待跟进事宜</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>给这六列起个名字。决策表里以 会议记录 为列名的输出格: 写 上期 = 组内每列从上期的同名列复制; 写 清空 = 整组清空; - = 不改。同一条规则显式写了的列以显式为准 (R1 的 例会时间, R3 的 状态-会议)</t>
         </is>
@@ -824,12 +821,12 @@
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>首次命中</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>三条规则互斥, 每行最多命中一条; 不冒泡且上批没有记录的岗位什么都不动。本批冒泡 是文本列, 格里的 是 / 否 是文字</t>
         </is>
@@ -842,229 +839,229 @@
       <c r="I1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="I2" s="15" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>本期.本批冒泡</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>上期.存在</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>上期.状态-会议</t>
         </is>
       </c>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>会议记录</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>例会时间</t>
         </is>
       </c>
-      <c r="H3" s="14" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>状态-会议</t>
         </is>
       </c>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>=基准日期</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>本批冒泡且上批有记录: 会议记录整组从上期带入, 例会时间改成本批例会日 (显式写的列优先于字段组里的同名列)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>=基准日期</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>首次冒泡: 记例会时间, 状态 01-新增</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>!= 05-已关闭</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>06-本批未冒泡</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>上批冒泡、本批没冒泡且上批还没关闭: 历史记录整组带入 (例会时间也是上批的), 状态标成 06。已关闭的不动</t>
         </is>
@@ -1084,10 +1081,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10.8" customWidth="1" min="1" max="1"/>
     <col width="16.2" customWidth="1" min="2" max="2"/>
     <col width="11.8" customWidth="1" min="3" max="3"/>
     <col width="16.2" customWidth="1" min="4" max="4"/>
@@ -1107,532 +1104,564 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>基准日期</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="n">
+        <v>46315</v>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>用例是按这个日期写的 (T1 / T2 / T5 期望的例会时间就是它), 只给内嵌测试用; 与「设置」和 --var 无关, 生产换批次日期不影响用例</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="4" t="n"/>
+      <c r="Q1" s="5" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
+      <c r="K2" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="L1" s="14" t="inlineStr">
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="M1" s="14" t="inlineStr">
+      <c r="M2" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="N1" s="14" t="inlineStr">
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="O1" s="14" t="inlineStr">
+      <c r="O2" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="P1" s="14" t="inlineStr">
+      <c r="P2" s="13" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="Q1" s="15" t="inlineStr">
+      <c r="Q2" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>本期.本批冒泡</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>上期.存在</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>上期.例会时间</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>上期.类别-会议</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>上期.状态-会议</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>上期.例会结论</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>上期.备注</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>上期.待跟进事宜</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>本期.备注</t>
         </is>
       </c>
-      <c r="K2" s="14" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t>例会时间</t>
         </is>
       </c>
-      <c r="L2" s="14" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>类别-会议</t>
         </is>
       </c>
-      <c r="M2" s="14" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t>状态-会议</t>
         </is>
       </c>
-      <c r="N2" s="14" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>例会结论</t>
         </is>
       </c>
-      <c r="O2" s="14" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="P2" s="14" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t>待跟进事宜</t>
         </is>
       </c>
-      <c r="Q2" s="15" t="inlineStr">
+      <c r="Q3" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D3" s="21" t="n">
+      <c r="D4" s="21" t="n">
         <v>46285</v>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>同意推进</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>候选人待定</t>
         </is>
       </c>
-      <c r="I3" s="17" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>确认任命时间</t>
         </is>
       </c>
-      <c r="J3" s="17" t="n"/>
-      <c r="K3" s="22" t="n">
-        <v>46315</v>
-      </c>
-      <c r="L3" s="18" t="inlineStr">
-        <is>
-          <t>变动通报</t>
-        </is>
-      </c>
-      <c r="M3" s="18" t="inlineStr">
-        <is>
-          <t>02-进展更新</t>
-        </is>
-      </c>
-      <c r="N3" s="18" t="inlineStr">
-        <is>
-          <t>同意推进</t>
-        </is>
-      </c>
-      <c r="O3" s="18" t="inlineStr">
-        <is>
-          <t>候选人待定</t>
-        </is>
-      </c>
-      <c r="P3" s="18" t="inlineStr">
-        <is>
-          <t>确认任命时间</t>
-        </is>
-      </c>
-      <c r="Q3" s="8" t="inlineStr">
-        <is>
-          <t>冒泡且上批有: 六列整组带入, 例会时间是本批的 (基准日期) 而不是上批的</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="n"/>
-      <c r="E4" s="17" t="n"/>
-      <c r="F4" s="17" t="n"/>
-      <c r="G4" s="17" t="n"/>
-      <c r="H4" s="17" t="n"/>
-      <c r="I4" s="17" t="n"/>
-      <c r="J4" s="17" t="n"/>
+      <c r="J4" s="16" t="n"/>
       <c r="K4" s="22" t="n">
         <v>46315</v>
       </c>
-      <c r="L4" s="18" t="n"/>
-      <c r="M4" s="18" t="inlineStr">
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>02-进展更新</t>
+        </is>
+      </c>
+      <c r="N4" s="17" t="inlineStr">
+        <is>
+          <t>同意推进</t>
+        </is>
+      </c>
+      <c r="O4" s="17" t="inlineStr">
+        <is>
+          <t>候选人待定</t>
+        </is>
+      </c>
+      <c r="P4" s="17" t="inlineStr">
+        <is>
+          <t>确认任命时间</t>
+        </is>
+      </c>
+      <c r="Q4" s="7" t="inlineStr">
+        <is>
+          <t>冒泡且上批有: 六列整组带入, 例会时间是本批的 (基准日期) 而不是上批的</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="n"/>
+      <c r="K5" s="22" t="n">
+        <v>46315</v>
+      </c>
+      <c r="L5" s="17" t="n"/>
+      <c r="M5" s="17" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="N4" s="18" t="n"/>
-      <c r="O4" s="18" t="n"/>
-      <c r="P4" s="18" t="n"/>
-      <c r="Q4" s="20" t="inlineStr">
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="17" t="n"/>
+      <c r="P5" s="17" t="n"/>
+      <c r="Q5" s="19" t="inlineStr">
         <is>
           <t>冒泡且上批没有: 首次冒泡</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D6" s="21" t="n">
         <v>46285</v>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>按计划</t>
         </is>
       </c>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="H6" s="16" t="n"/>
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>跟进到位情况</t>
         </is>
       </c>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="22" t="n">
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="22" t="n">
         <v>46285</v>
       </c>
-      <c r="L5" s="18" t="inlineStr">
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="M5" s="18" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>06-本批未冒泡</t>
         </is>
       </c>
-      <c r="N5" s="18" t="inlineStr">
+      <c r="N6" s="17" t="inlineStr">
         <is>
           <t>按计划</t>
         </is>
       </c>
-      <c r="O5" s="18" t="n"/>
-      <c r="P5" s="18" t="inlineStr">
+      <c r="O6" s="17" t="n"/>
+      <c r="P6" s="17" t="inlineStr">
         <is>
           <t>跟进到位情况</t>
         </is>
       </c>
-      <c r="Q5" s="8" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>不冒泡且上批有未关闭记录: 整组带入, 例会时间是上批的, 状态标 06</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="17" t="n"/>
-      <c r="H6" s="17" t="n"/>
-      <c r="I6" s="17" t="n"/>
-      <c r="J6" s="17" t="n"/>
-      <c r="K6" s="18" t="n"/>
-      <c r="L6" s="18" t="n"/>
-      <c r="M6" s="18" t="n"/>
-      <c r="N6" s="18" t="n"/>
-      <c r="O6" s="18" t="n"/>
-      <c r="P6" s="18" t="n"/>
-      <c r="Q6" s="20" t="inlineStr">
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="19" t="inlineStr">
         <is>
           <t>不冒泡且上批没有: 不动</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D8" s="21" t="n">
         <v>46285</v>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>面谈通过</t>
         </is>
       </c>
-      <c r="H7" s="17" t="n"/>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>走审批</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>临时备注</t>
         </is>
       </c>
-      <c r="K7" s="22" t="n">
+      <c r="K8" s="22" t="n">
         <v>46315</v>
       </c>
-      <c r="L7" s="18" t="inlineStr">
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="M7" s="18" t="inlineStr">
+      <c r="M8" s="17" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="N7" s="18" t="inlineStr">
+      <c r="N8" s="17" t="inlineStr">
         <is>
           <t>面谈通过</t>
         </is>
       </c>
-      <c r="O7" s="18" t="inlineStr">
+      <c r="O8" s="17" t="inlineStr">
         <is>
           <t>空</t>
         </is>
       </c>
-      <c r="P7" s="18" t="inlineStr">
+      <c r="P8" s="17" t="inlineStr">
         <is>
           <t>走审批</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="Q8" s="7" t="inlineStr">
         <is>
           <t>本期备注原来有值、上期为空: 整组带入会把它清成空 (期望格写 空)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>05-已关闭</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>已任命</t>
         </is>
       </c>
-      <c r="H8" s="17" t="n"/>
-      <c r="I8" s="17" t="n"/>
-      <c r="J8" s="17" t="n"/>
-      <c r="K8" s="18" t="n"/>
-      <c r="L8" s="18" t="n"/>
-      <c r="M8" s="18" t="n"/>
-      <c r="N8" s="18" t="n"/>
-      <c r="O8" s="18" t="n"/>
-      <c r="P8" s="18" t="n"/>
-      <c r="Q8" s="20" t="inlineStr">
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="17" t="n"/>
+      <c r="L9" s="17" t="n"/>
+      <c r="M9" s="17" t="n"/>
+      <c r="N9" s="17" t="n"/>
+      <c r="O9" s="17" t="n"/>
+      <c r="P9" s="17" t="n"/>
+      <c r="Q9" s="19" t="inlineStr">
         <is>
           <t>不冒泡且上批已关闭: R3 的 != 05-已关闭 不成立, 不动</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:Q1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>